--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260626.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260626.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.04%</t>
+          <t>10.35%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.93%</t>
+          <t>10.16%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.71%</t>
+          <t>6.60%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.28%</t>
+          <t>5.03%</t>
         </is>
       </c>
     </row>
@@ -704,73 +704,73 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.55%</t>
+          <t>4.42%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>4,979,000</t>
+          <t>112,174,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.38%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>25,748,000</t>
+          <t>4,979,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>112,174,000</t>
+          <t>25,748,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
@@ -792,51 +792,51 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>133,920,945</t>
+          <t>569,427,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>569,427,000</t>
+          <t>133,920,945</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
@@ -858,51 +858,51 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>30,366,000</t>
+          <t>25,824,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>25,824,000</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
@@ -924,24 +924,24 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>144,292,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,22 +953,22 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>144,292,000</t>
+          <t>30,366,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -1122,46 +1122,46 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>178,956,000</t>
+          <t>269,366,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>269,366,000</t>
+          <t>51,717,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>51,717,000</t>
+          <t>178,956,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,067,574,235</t>
+          <t>5,672,010,141</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>10,966,030,103</t>
+          <t>10,230,650,103</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-592,290,360</t>
+          <t>-202,261,844</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
